--- a/artfynd/A 34304-2025 artfynd.xlsx
+++ b/artfynd/A 34304-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126017300</v>
+        <v>126379699</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743360</v>
+        <v>742984</v>
       </c>
       <c r="R2" t="n">
-        <v>7327164</v>
+        <v>7326591</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>126017296</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379703</v>
+        <v>126017300</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743230</v>
+        <v>743360</v>
       </c>
       <c r="R4" t="n">
-        <v>7327061</v>
+        <v>7327164</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126379699</v>
+        <v>126379701</v>
       </c>
       <c r="B5" t="n">
-        <v>92527</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742984</v>
+        <v>743208</v>
       </c>
       <c r="R5" t="n">
-        <v>7326591</v>
+        <v>7326960</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126379701</v>
+        <v>126379703</v>
       </c>
       <c r="B6" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743208</v>
+        <v>743230</v>
       </c>
       <c r="R6" t="n">
-        <v>7326960</v>
+        <v>7327061</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1208,7 @@
         <v>126379702</v>
       </c>
       <c r="B7" t="n">
-        <v>97239</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2025 artfynd.xlsx
+++ b/artfynd/A 34304-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017296</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017300</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379701</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379703</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379702</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>